--- a/SHARC_tests3.xlsx
+++ b/SHARC_tests3.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smhhborg\Desktop\test for SHARC Crosswalks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\smhhborg(D_Laufwerk)\Documents\GitHub\test_for_shacl_shape_bridges\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11850" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11850" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Curies" sheetId="1" r:id="rId1"/>
